--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-07-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95900E6E-315A-4EF1-8E09-5244B0552D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8507949-70C6-4DAA-B59A-64FC240AFA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4125" yWindow="915" windowWidth="21600" windowHeight="12750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="180" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -943,30 +943,6 @@
     <t>£38.60</t>
   </si>
   <si>
-    <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff61d9fa865+152a5]
-	chromedriver!GetHandleVerifier [0x7ff61d9fa8c0+15300]
-	chromedriver!(No symbol) [0x7ff61d55596d]
-	chromedriver!(No symbol) [0x7ff61d5b05a9]
-	chromedriver!(No symbol) [0x7ff61d5b08ac]
-	chromedriver!(No symbol) [0x7ff61d6010f7]
-	chromedriver!(No symbol) [0x7ff61d5fdcf4]
-	chromedriver!(No symbol) [0x7ff61d5a2b3c]
-	chromedriver!(No symbol) [0x7ff61d5a3a53]
-	chromedriver!GetHandleVerifier [0x7ff61dfdd3a1+5f7de1]
-	chromedriver!GetHandleVerifier [0x7ff61dfd7a3b+5f247b]
-	chromedriver!GetHandleVerifier [0x7ff61dffbca5+6166e5]
-	chromedriver!GetHandleVerifier [0x7ff61da172ae+31cee]
-	chromedriver!GetHandleVerifier [0x7ff61da1fe3c+3a87c]
-	chromedriver!GetHandleVerifier [0x7ff61da04404+1ee44]
-	chromedriver!GetHandleVerifier [0x7ff61da04594+1efd4]
-	chromedriver!GetHandleVerifier [0x7ff61d9e75c7+2007]
-	KERNEL32!BaseThreadInitThunk [0x7ff96b10e957+17]
-	ntdll!RtlUserThreadStart [0x7ff96d147c1c+2c]
-</t>
-  </si>
-  <si>
     <t>£41.28</t>
   </si>
   <si>
@@ -1226,6 +1202,9 @@
   </si>
   <si>
     <t>£19.49</t>
+  </si>
+  <si>
+    <t>£40.45</t>
   </si>
 </sst>
 </file>
@@ -1669,7 +1648,7 @@
         <v>74</v>
       </c>
       <c r="F2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G2" t="s">
         <v>103</v>
@@ -1693,7 +1672,7 @@
         <v>221</v>
       </c>
       <c r="N2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O2" t="s">
         <v>250</v>
@@ -1705,7 +1684,7 @@
         <v>300</v>
       </c>
       <c r="R2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1725,7 +1704,7 @@
         <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G3" t="s">
         <v>104</v>
@@ -1749,7 +1728,7 @@
         <v>222</v>
       </c>
       <c r="N3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O3" t="s">
         <v>251</v>
@@ -1761,7 +1740,7 @@
         <v>301</v>
       </c>
       <c r="R3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1772,16 +1751,16 @@
         <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G4" t="s">
         <v>105</v>
@@ -1805,7 +1784,7 @@
         <v>223</v>
       </c>
       <c r="N4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O4" t="s">
         <v>252</v>
@@ -1817,7 +1796,7 @@
         <v>302</v>
       </c>
       <c r="R4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1837,7 +1816,7 @@
         <v>76</v>
       </c>
       <c r="F5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G5" t="s">
         <v>106</v>
@@ -1861,7 +1840,7 @@
         <v>224</v>
       </c>
       <c r="N5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O5" t="s">
         <v>253</v>
@@ -1873,7 +1852,7 @@
         <v>76</v>
       </c>
       <c r="R5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1893,7 +1872,7 @@
         <v>77</v>
       </c>
       <c r="F6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G6" t="s">
         <v>107</v>
@@ -1917,7 +1896,7 @@
         <v>225</v>
       </c>
       <c r="N6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="O6" t="s">
         <v>254</v>
@@ -1929,7 +1908,7 @@
         <v>303</v>
       </c>
       <c r="R6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1949,7 +1928,7 @@
         <v>78</v>
       </c>
       <c r="F7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G7" t="s">
         <v>108</v>
@@ -1973,7 +1952,7 @@
         <v>226</v>
       </c>
       <c r="N7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O7" t="s">
         <v>255</v>
@@ -1985,7 +1964,7 @@
         <v>304</v>
       </c>
       <c r="R7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -2005,7 +1984,7 @@
         <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G8" t="s">
         <v>108</v>
@@ -2029,7 +2008,7 @@
         <v>227</v>
       </c>
       <c r="N8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O8" t="s">
         <v>255</v>
@@ -2041,7 +2020,7 @@
         <v>305</v>
       </c>
       <c r="R8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -2061,7 +2040,7 @@
         <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G9" t="s">
         <v>109</v>
@@ -2085,7 +2064,7 @@
         <v>228</v>
       </c>
       <c r="N9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O9" t="s">
         <v>256</v>
@@ -2097,7 +2076,7 @@
         <v>306</v>
       </c>
       <c r="R9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -2117,7 +2096,7 @@
         <v>81</v>
       </c>
       <c r="F10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G10" t="s">
         <v>110</v>
@@ -2141,7 +2120,7 @@
         <v>229</v>
       </c>
       <c r="N10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O10" t="s">
         <v>257</v>
@@ -2150,10 +2129,10 @@
         <v>283</v>
       </c>
       <c r="Q10" t="s">
-        <v>307</v>
+        <v>394</v>
       </c>
       <c r="R10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -2173,7 +2152,7 @@
         <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G11" t="s">
         <v>111</v>
@@ -2197,7 +2176,7 @@
         <v>230</v>
       </c>
       <c r="N11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O11" t="s">
         <v>258</v>
@@ -2206,10 +2185,10 @@
         <v>284</v>
       </c>
       <c r="Q11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="R11" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -2229,7 +2208,7 @@
         <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G12" t="s">
         <v>83</v>
@@ -2253,7 +2232,7 @@
         <v>231</v>
       </c>
       <c r="N12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O12" t="s">
         <v>259</v>
@@ -2262,10 +2241,10 @@
         <v>83</v>
       </c>
       <c r="Q12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -2285,7 +2264,7 @@
         <v>84</v>
       </c>
       <c r="F13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G13" t="s">
         <v>112</v>
@@ -2309,7 +2288,7 @@
         <v>232</v>
       </c>
       <c r="N13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O13" t="s">
         <v>260</v>
@@ -2318,10 +2297,10 @@
         <v>285</v>
       </c>
       <c r="Q13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="R13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -2341,7 +2320,7 @@
         <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G14" t="s">
         <v>113</v>
@@ -2365,7 +2344,7 @@
         <v>233</v>
       </c>
       <c r="N14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O14" t="s">
         <v>261</v>
@@ -2374,7 +2353,7 @@
         <v>286</v>
       </c>
       <c r="Q14" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="R14" t="s">
         <v>141</v>
@@ -2394,10 +2373,10 @@
         <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="F15" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G15" t="s">
         <v>114</v>
@@ -2430,7 +2409,7 @@
         <v>287</v>
       </c>
       <c r="Q15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="R15" t="s">
         <v>101</v>
@@ -2453,7 +2432,7 @@
         <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G16" t="s">
         <v>115</v>
@@ -2477,7 +2456,7 @@
         <v>235</v>
       </c>
       <c r="N16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="O16" t="s">
         <v>263</v>
@@ -2486,10 +2465,10 @@
         <v>288</v>
       </c>
       <c r="Q16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2509,7 +2488,7 @@
         <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G17" t="s">
         <v>101</v>
@@ -2533,7 +2512,7 @@
         <v>236</v>
       </c>
       <c r="N17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O17" t="s">
         <v>264</v>
@@ -2542,7 +2521,7 @@
         <v>289</v>
       </c>
       <c r="Q17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="R17" t="s">
         <v>101</v>
@@ -2565,7 +2544,7 @@
         <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G18" t="s">
         <v>116</v>
@@ -2589,7 +2568,7 @@
         <v>237</v>
       </c>
       <c r="N18" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O18" t="s">
         <v>265</v>
@@ -2598,10 +2577,10 @@
         <v>290</v>
       </c>
       <c r="Q18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="R18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -2621,7 +2600,7 @@
         <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G19" t="s">
         <v>117</v>
@@ -2645,7 +2624,7 @@
         <v>238</v>
       </c>
       <c r="N19" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O19" t="s">
         <v>266</v>
@@ -2654,10 +2633,10 @@
         <v>291</v>
       </c>
       <c r="Q19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="R19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2677,7 +2656,7 @@
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -2701,7 +2680,7 @@
         <v>239</v>
       </c>
       <c r="N20" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O20" t="s">
         <v>267</v>
@@ -2710,10 +2689,10 @@
         <v>292</v>
       </c>
       <c r="Q20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="R20" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -2733,7 +2712,7 @@
         <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G21" t="s">
         <v>119</v>
@@ -2757,7 +2736,7 @@
         <v>240</v>
       </c>
       <c r="N21" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O21" t="s">
         <v>268</v>
@@ -2766,10 +2745,10 @@
         <v>293</v>
       </c>
       <c r="Q21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R21" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -2789,7 +2768,7 @@
         <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G22" t="s">
         <v>120</v>
@@ -2813,7 +2792,7 @@
         <v>241</v>
       </c>
       <c r="N22" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O22" t="s">
         <v>269</v>
@@ -2822,10 +2801,10 @@
         <v>93</v>
       </c>
       <c r="Q22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -2845,7 +2824,7 @@
         <v>94</v>
       </c>
       <c r="F23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G23" t="s">
         <v>101</v>
@@ -2869,7 +2848,7 @@
         <v>242</v>
       </c>
       <c r="N23" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="O23" t="s">
         <v>270</v>
@@ -2878,10 +2857,10 @@
         <v>294</v>
       </c>
       <c r="Q23" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="R23" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2901,7 +2880,7 @@
         <v>95</v>
       </c>
       <c r="F24" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G24" t="s">
         <v>101</v>
@@ -2925,7 +2904,7 @@
         <v>243</v>
       </c>
       <c r="N24" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="O24" t="s">
         <v>271</v>
@@ -2934,10 +2913,10 @@
         <v>295</v>
       </c>
       <c r="Q24" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="R24" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -3013,7 +2992,7 @@
         <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G26" t="s">
         <v>101</v>
@@ -3037,7 +3016,7 @@
         <v>245</v>
       </c>
       <c r="N26" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O26" t="s">
         <v>273</v>
@@ -3046,10 +3025,10 @@
         <v>296</v>
       </c>
       <c r="Q26" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="R26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -3069,7 +3048,7 @@
         <v>98</v>
       </c>
       <c r="F27" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G27" t="s">
         <v>101</v>
@@ -3093,7 +3072,7 @@
         <v>246</v>
       </c>
       <c r="N27" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="O27" t="s">
         <v>274</v>
@@ -3102,10 +3081,10 @@
         <v>297</v>
       </c>
       <c r="Q27" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="R27" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -3125,7 +3104,7 @@
         <v>99</v>
       </c>
       <c r="F28" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G28" t="s">
         <v>101</v>
@@ -3149,7 +3128,7 @@
         <v>247</v>
       </c>
       <c r="N28" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O28" t="s">
         <v>275</v>
@@ -3158,10 +3137,10 @@
         <v>298</v>
       </c>
       <c r="Q28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R28" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -3181,7 +3160,7 @@
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G29" t="s">
         <v>101</v>
@@ -3205,7 +3184,7 @@
         <v>248</v>
       </c>
       <c r="N29" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O29" t="s">
         <v>276</v>
@@ -3217,7 +3196,7 @@
         <v>101</v>
       </c>
       <c r="R29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
